--- a/reports/一级子公司A_现金流量表_2025-10.xlsx
+++ b/reports/一级子公司A_现金流量表_2025-10.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>155610000</v>
+        <v>155075283</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1505712000</v>
+        <v>1504373450</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3151557</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>30461154</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1571631</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>15200785</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>785395</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>7614385</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>630613</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>6082207</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>469947</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>4566480</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>315957</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>3042874</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>234695</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2281799</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>158006</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1522372</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>391492</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>3800967</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>198167</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1913483</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>124792</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1208248</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>399000</v>
+        <v>399004</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>3860800</v>
+        <v>3864467</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2835000</v>
+        <v>2839497</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>27432000</v>
+        <v>27409838</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>158844000</v>
+        <v>166346036</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>100800000</v>
+        <v>100331193</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>975360000</v>
+        <v>974756704</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1052327</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>10152204</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>784201</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>7600488</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>524734</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>5076889</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>393325</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>3800429</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>261535</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>2537819</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>198244</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1910761</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16485000</v>
+        <v>16412361</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>159512000</v>
+        <v>159542721</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8400000</v>
+        <v>8441413</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>81280000</v>
+        <v>81290418</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3465000</v>
+        <v>3447889</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>33528000</v>
+        <v>33513399</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>129150000</v>
+        <v>131847222</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>29694000</v>
+        <v>34498814</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>180000</v>
+        <v>179318</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1800000</v>
+        <v>1800764</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1500000</v>
+        <v>1492515</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>15000000</v>
+        <v>14996503</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>920000</v>
+        <v>924442</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>9200000</v>
+        <v>9205003</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1680000</v>
+        <v>1671833</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14000000</v>
+        <v>14042793</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>140000000</v>
+        <v>140135425</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2000000</v>
+        <v>1996732</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>20000000</v>
+        <v>19979274</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10000000</v>
+        <v>10000409</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>100000000</v>
+        <v>100099704</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>380000</v>
+        <v>378174</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>3800000</v>
+        <v>3799967</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14380000</v>
+        <v>14420967</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-12700000</v>
+        <v>-12749134</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3500000</v>
+        <v>3490830</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>35000000</v>
+        <v>34964947</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5500000</v>
+        <v>5502691</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>55000000</v>
+        <v>54947142</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5500000</v>
+        <v>5488716</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>55000000</v>
+        <v>55043236</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>180000</v>
+        <v>180612</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1800000</v>
+        <v>1799048</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9180000</v>
+        <v>9174133</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4500000</v>
+        <v>4522162</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>45000000</v>
+        <v>45005329</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4500000</v>
+        <v>4477756</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>45000000</v>
+        <v>44980152</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>720000</v>
+        <v>723200</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>7200000</v>
+        <v>7205168</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>630000</v>
+        <v>631357</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>6300000</v>
+        <v>6306455</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>90000</v>
+        <v>89946</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>900000</v>
+        <v>899080</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5310000</v>
+        <v>5335308</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3870000</v>
+        <v>3838825</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>20864000</v>
+        <v>25588505</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>20864000</v>
+        <v>25588505</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
